--- a/stories/arbres/TREE-EMO-001.xlsx
+++ b/stories/arbres/TREE-EMO-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>À l'école, Maya range son manteau. Maman l'a accompagnée jusqu'à la porte. Dans la cour, Léa lui montre un dessin. Maya sent les joues chaudes. La poitrine est légère. Maya a envie de sourire. Papa viendra ce soir. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>À l'école, Maya range son manteau. Maman l'a accompagnée jusqu'à la porte. Dans la cour, Léa lui montre un dessin. Maya sent les joues chaudes. La poitrine est légère. Maya a envie de sourire. Papa viendra ce soir. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|À l'école, Maya range son manteau. Maman l'a accompagnée jusqu'à la porte. Dans la cour, Léa lui montre un dessin. Maya sent les joues chaudes. La poitrine est légère. Maya a envie de sourire. Papa viendra ce soir. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa partage une pomme au goûter. Maya sent la joie monter. C'est une pomme. Le sable est un peu frais. Maya s'approche, sans courir. Papa n'est pas loin. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Léa partage une pomme au goûter. Maya sent la joie monter. C'est une pomme. Le sable est un peu frais. Maya s'approche, sans courir. Papa n'est pas loin. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa partage une pomme au goûter. Maya sent la joie monter. C'est une pomme. Le sable est un peu frais. Maya s'approche, sans courir. Papa n'est pas loin. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1863,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a les joues chaudes. Quel mot dit-on ? Avec une pomme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1851,7 +1892,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya retient le geste. Elle respire.</t>
+          <t>Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya retient le geste. Elle respire.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1993,6 +2034,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2227,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,7 +2256,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la cuisine, après une pomme. La terre est un peu humide. Maya range un peu autour de la cuisine. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi la cuisine, après une pomme. La terre est un peu humide. Maya range un peu autour de la cuisine. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2341,6 +2394,13 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine, après une pomme. La terre est un peu humide. Maya range un peu autour de la cuisine. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2587,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2551,7 +2616,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après une pomme et la cuisine. La tasse est encore tiède. On dit merci. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On laisse les cubes à sa place. Maya est près de maman. Le soleil est encore là.</t>
+          <t>Maya rejoint les cubes, après une pomme et la cuisine. La tasse est encore tiède. On dit merci. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On laisse les cubes à sa place. Maya est près de maman. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2689,6 +2754,13 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après une pomme et la cuisine. La tasse est encore tiède. On dit merci. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On laisse les cubes à sa place. Maya est près de maman. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2923,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2875,7 +2952,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après une pomme et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On gardu geste.</t>
+          <t>Maya rejoint le livre, après une pomme et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On gardu geste.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3013,6 +3090,13 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après une pomme et la cuisine. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3259,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3199,7 +3288,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maman dit : je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
+          <t>Maya rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3337,6 +3426,14 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après une pomme et la cuisine. Une abeille bourdonne loin. On attend un petit moment. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.
+maman|Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3596,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3523,7 +3625,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le jardin, après une pomme. Une abeille bourdonne loin. Maya s'installe avec le jardin. Maman reste à portée de voix. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi le jardin, après une pomme. Une abeille bourdonne loin. Maya s'installe avec le jardin. Maman reste à portée de voix. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3661,6 +3763,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin, après une pomme. Une abeille bourdonne loin. Maya s'installe avec le jardin. Maman reste à portée de voix. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3956,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3871,7 +3985,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après une pomme et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On laisse les cubes à sa place. Maya est près de maman. On respire.</t>
+          <t>Maya rejoint les cubes, après une pomme et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On laisse les cubes à sa place. Maya est près de maman. On respire.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4009,6 +4123,13 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après une pomme et le jardin. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On laisse les cubes à sa place. Maya est près de maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4292,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4195,7 +4321,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après une pomme et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Merci, et au dodo bientôt.</t>
+          <t>Maya rejoint le livre, après une pomme et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4333,6 +4459,13 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après une pomme et le jardin. La fenêtre tremble un tout petit peu. On sourit un peu. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4628,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4519,7 +4657,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maman dit : je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
+          <t>Maya rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4657,6 +4795,15 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après une pomme et le jardin. Ça sent le savon de maman. On boit une gorgée d'eau. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4966,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4843,7 +4995,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la chambre, après une pomme. Un papillon passe sans bruit. Maya attend près de la chambre. Elle ne prend pas de force. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi la chambre, après une pomme. Un papillon passe sans bruit. Maya attend près de la chambre. Elle ne prend pas de force. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4981,6 +5133,13 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre, après une pomme. Un papillon passe sans bruit. Maya attend près de la chambre. Elle ne prend pas de force. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5326,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5191,7 +5355,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après une pomme et la chambre. Un pigeon roucoule. On essuie une miette. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On se serre un peu.</t>
+          <t>Maya rejoint les cubes, après une pomme et la chambre. Un pigeon roucoule. On essuie une miette. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On se serre un peu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5329,6 +5493,13 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après une pomme et la chambre. Un pigeon roucoule. On essuie une miette. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5662,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5515,7 +5691,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après une pomme et la chambre. La cuillère tinte. On referme un livre. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. On rentre.</t>
+          <t>Maya rejoint le livre, après une pomme et la chambre. La cuillère tinte. On referme un livre. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. On rentre.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5653,6 +5829,13 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après une pomme et la chambre. La cuillère tinte. On referme un livre. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5998,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5839,7 +6027,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après une pomme et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya pose la dînette et va vers maman. La journée continue, tout doux.</t>
+          <t>Maya rejoint la dînette, après une pomme et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya pose la dînette et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5977,6 +6165,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après une pomme et la chambre. Le ballon est un peu poudreux. On pose un jouet à sa place. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya pose la dînette et va vers maman. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6334,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6363,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Un yaourt arrive, frais. Maya a envie d'inviter une copine. Maya s'occupe de un yaourt. Le soleil chauffe un peu le nez. Maman sourit. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Un yaourt arrive, frais. Maya a envie d'inviter une copine. Maya s'occupe de un yaourt. Le soleil chauffe un peu le nez. Maman sourit. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6501,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Un yaourt arrive, frais. Maya a envie d'inviter une copine. Maya s'occupe de un yaourt. Le soleil chauffe un peu le nez. Maman sourit. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6479,6 +6686,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a les joues chaudes. Quel mot dit-on ? Avec un yaourt.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6503,7 +6715,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya répète le mot. Maman hoche la tête.</t>
+          <t>Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6645,6 +6857,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya répète le mot. Maman hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7050,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6855,7 +7079,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la cuisine, après un yaourt. La lumière est douce et claire. Maya touche la cuisine tout doucement. Maman dit : je suis là. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi la cuisine, après un yaourt. La lumière est douce et claire. Maya touche la cuisine tout doucement. Je suis là. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -6993,6 +7217,15 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine, après un yaourt. La lumière est douce et claire. Maya touche la cuisine tout doucement.
+maman|Je suis là.
+narrateur|Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7412,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7203,7 +7441,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après un yaourt et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On se dit à plus tard.</t>
+          <t>Maya rejoint les cubes, après un yaourt et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7341,6 +7579,13 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après un yaourt et la cuisine. Une goutte de pluie sèche déjà. On marche tout doucement. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7748,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7527,7 +7777,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maman dit : je t'ai entendu. Papa aussi. Le soleil est encore là.</t>
+          <t>Maya rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Je t'ai entendu. Papa aussi. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7665,6 +7915,15 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après un yaourt et la cuisine. Le banc est tiède. On se tait une seconde. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8086,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7851,7 +8115,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après un yaourt et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On laisse la dînette à sa place. Maya est près de maman. On gardu geste.</t>
+          <t>Maya rejoint la dînette, après un yaourt et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On laisse la dînette à sa place. Maya est près de maman. On gardu geste.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -7989,6 +8253,13 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après un yaourt et la cuisine. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On laisse la dînette à sa place. Maya est près de maman. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8422,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8175,7 +8451,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le jardin, après un yaourt. L'eau fait un tout petit bruit. Maya montre le jardin à maman. Elle nomme ce qu'elle sent. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi le jardin, après un yaourt. L'eau fait un tout petit bruit. Maya montre le jardin à maman. Elle nomme ce qu'elle sent. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8313,6 +8589,13 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin, après un yaourt. L'eau fait un tout petit bruit. Maya montre le jardin à maman. Elle nomme ce qu'elle sent. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8782,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8523,7 +8811,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après un yaourt et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Papa et maman sont là.</t>
+          <t>Maya rejoint les cubes, après un yaourt et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8661,6 +8949,13 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après un yaourt et le jardin. Une feuille tourne et tombe. On s'assoit près de l'adulte. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9118,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8847,7 +9147,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après un yaourt et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya pose le livre et va vers maman. On respire.</t>
+          <t>Maya rejoint le livre, après un yaourt et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya pose le livre et va vers maman. On respire.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -8985,6 +9285,13 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après un yaourt et le jardin. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya pose le livre et va vers maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9454,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9171,7 +9483,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après un yaourt et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. Merci, et au dodo bientôt.</t>
+          <t>Maya rejoint la dînette, après un yaourt et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9309,6 +9621,13 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après un yaourt et le jardin. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9790,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9495,7 +9819,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la chambre, après un yaourt. Le toboggan est un peu froid. Maya range un peu autour de la chambre. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi la chambre, après un yaourt. Le toboggan est un peu froid. Maya range un peu autour de la chambre. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9633,6 +9957,13 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre, après un yaourt. Le toboggan est un peu froid. Maya range un peu autour de la chambre. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10150,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9843,7 +10179,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après un yaourt et la chambre. Une plume vole. On range les chaussures. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
+          <t>Maya rejoint les cubes, après un yaourt et la chambre. Une plume vole. On range les chaussures. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9981,6 +10317,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après un yaourt et la chambre. Une plume vole. On range les chaussures. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10486,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10167,7 +10515,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après un yaourt et la chambre. Le pain croustille. On met le doudou près de soi. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya pose le livre et va vers maman. On se serre un peu.</t>
+          <t>Maya rejoint le livre, après un yaourt et la chambre. Le pain croustille. On met le doudou près de soi. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya pose le livre et va vers maman. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10305,6 +10653,13 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après un yaourt et la chambre. Le pain croustille. On met le doudou près de soi. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya pose le livre et va vers maman. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10822,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10491,7 +10851,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après un yaourt et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On rentre.</t>
+          <t>Maya rejoint la dînette, après un yaourt et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On rentre.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10629,6 +10989,13 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après un yaourt et la chambre. La laine du doudou est douce. On écoute le cœur, tout doux. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11158,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11187,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Un morceau de pain croustille. Maya veut partager le bruit drôle. Voilà un morceau de pain. Un coq chante une fois. Maya pose les pieds par terre, près de maman. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Un morceau de pain croustille. Maya veut partager le bruit drôle. Voilà un morceau de pain. Un coq chante une fois. Maya pose les pieds par terre, près de maman. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11325,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain croustille. Maya veut partager le bruit drôle. Voilà un morceau de pain. Un coq chante une fois. Maya pose les pieds par terre, près de maman. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11131,6 +11510,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a les joues chaudes. Quel mot dit-on ? Avec un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11155,7 +11539,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya pose les pieds par terre. On continue, tout calme.</t>
+          <t>Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11297,6 +11681,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11874,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11507,7 +11903,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la cuisine, après un morceau de pain. Un coq chante une fois. Maya range un peu autour de la cuisine. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi la cuisine, après un morceau de pain. Un coq chante une fois. Maya range un peu autour de la cuisine. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11645,6 +12041,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la cuisine, après un morceau de pain. Un coq chante une fois. Maya range un peu autour de la cuisine. Elle respire. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12234,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11855,7 +12263,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après un morceau de pain et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. La journée continue, tout doux.</t>
+          <t>Maya rejoint les cubes, après un morceau de pain et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -11993,6 +12401,13 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après un morceau de pain et la cuisine. Un galet est lisse dans la main. On secoue les mains, loin. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12570,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12179,7 +12599,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après un morceau de pain et la cuisine. Le train souffle au loin. On pose le sac. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On se dit à plus tard.</t>
+          <t>Maya rejoint le livre, après un morceau de pain et la cuisine. Le train souffle au loin. On pose le sac. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12317,6 +12737,13 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après un morceau de pain et la cuisine. Le train souffle au loin. On pose le sac. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12906,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12503,7 +12935,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après un morceau de pain et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya range la dînette un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+          <t>Maya rejoint la dînette, après un morceau de pain et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya range la dînette un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12641,6 +13073,13 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après un morceau de pain et la cuisine. Une vache meugle, loin. On dit le mot de l'émotion. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya range la dînette un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13242,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12827,7 +13271,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi le jardin, après un morceau de pain. Le ballon est un peu poudreux. On parle du jardin. Maya écoute jusqu'au bout. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi le jardin, après un morceau de pain. Le ballon est un peu poudreux. On parle du jardin. Maya écoute jusqu'au bout. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12965,6 +13409,13 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le jardin, après un morceau de pain. Le ballon est un peu poudreux. On parle du jardin. Maya écoute jusqu'au bout. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13602,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13175,7 +13631,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maman dit : je t'ai entendu. Papa aussi. On gardu geste.</t>
+          <t>Maya rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Je t'ai entendu. Papa aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13313,6 +13769,14 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après un morceau de pain et le jardin. Un grillon chante, tout petit. On invite d'une petite voix. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.
+maman|Je t'ai entendu. Papa aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13939,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13499,7 +13968,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après un morceau de pain et le jardin. Le bois de la table est lisse. On attend la réponse. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Papa et maman sont là.</t>
+          <t>Maya rejoint le livre, après un morceau de pain et le jardin. Le bois de la table est lisse. On attend la réponse. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13637,6 +14106,13 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après un morceau de pain et le jardin. Le bois de la table est lisse. On attend la réponse. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14275,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13823,7 +14304,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après un morceau de pain et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On respire.</t>
+          <t>Maya rejoint la dînette, après un morceau de pain et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On respire.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13961,6 +14442,13 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après un morceau de pain et le jardin. Une goutte tombe dans l'évier. On propose une autre idée. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14611,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14147,7 +14640,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Maya a choisi la chambre, après un morceau de pain. La terre est un peu humide. Maya attend près de la chambre. Elle ne prend pas de force. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager.</t>
+          <t>Maya a choisi la chambre, après un morceau de pain. La terre est un peu humide. Maya attend près de la chambre. Elle ne prend pas de force. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14285,6 +14778,13 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la chambre, après un morceau de pain. La terre est un peu humide. Maya attend près de la chambre. Elle ne prend pas de force. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14971,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14495,7 +15000,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint les cubes, après un morceau de pain et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
+          <t>Maya rejoint les cubes, après un morceau de pain et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14633,6 +15138,13 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les cubes, après un morceau de pain et la chambre. Le toboggan est un peu froid. On va vers papa ou maman. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15307,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14819,7 +15336,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint le livre, après un morceau de pain et la chambre. La clochette de la porte tinte. On dit stop, tout clair. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. Maya boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
+          <t>Maya rejoint le livre, après un morceau de pain et la chambre. La clochette de la porte tinte. On dit stop, tout clair. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. Maya boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14957,6 +15474,13 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le livre, après un morceau de pain et la chambre. La clochette de la porte tinte. On dit stop, tout clair. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. Maya boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15643,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15143,7 +15672,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Maya rejoint la dînette, après un morceau de pain et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Maya dit : je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On se serre un peu.</t>
+          <t>Maya rejoint la dînette, après un morceau de pain et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère. Je suis contente. Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On se serre un peu.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15281,6 +15810,13 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint la dînette, après un morceau de pain et la chambre. Ça sent le thym du jardin. On s'éloigne d'un pas. Maya se sent contente. C'est de la joie. Les joues sont chaudes. La poitrine est légère.
+enfant-f|Je suis contente.
+narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15979,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +16019,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-001.xlsx
+++ b/stories/arbres/TREE-EMO-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Maya a les joues chaudes. Quel mot dit-on ? Avec une pomme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2412,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2604,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2761,6 +2774,7 @@
 narrateur|Elle sourit. Elle invite à partager. On laisse les cubes à sa place. Maya est près de maman. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2928,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3112,7 @@
 narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3434,6 +3451,7 @@
 maman|Je t'ai entendu. Papa aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3601,6 +3619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3770,6 +3789,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3961,6 +3981,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4130,6 +4151,7 @@
 narrateur|Elle sourit. Elle invite à partager. On laisse les cubes à sa place. Maya est près de maman. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4297,6 +4319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4466,6 +4489,7 @@
 narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4633,6 +4657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4804,6 +4829,7 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4971,6 +4997,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5140,6 +5167,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5331,6 +5359,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5500,6 +5529,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5667,6 +5697,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5836,6 +5867,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6003,6 +6035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6172,6 +6205,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya pose la dînette et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6339,6 +6373,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6508,6 +6543,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6691,6 +6727,7 @@
           <t>narrateur|Maya a les joues chaudes. Quel mot dit-on ? Avec un yaourt.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6864,6 +6901,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7055,6 +7093,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7226,6 +7265,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7417,6 +7457,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7586,6 +7627,7 @@
 narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7753,6 +7795,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7924,6 +7967,7 @@
 narrateur|Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8091,6 +8135,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8260,6 +8305,7 @@
 narrateur|Elle sourit. Elle invite à partager. On laisse la dînette à sa place. Maya est près de maman. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8427,6 +8473,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8596,6 +8643,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8787,6 +8835,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8956,6 +9005,7 @@
 narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9123,6 +9173,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9292,6 +9343,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya pose le livre et va vers maman. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9459,6 +9511,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9628,6 +9681,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9795,6 +9849,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9964,6 +10019,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10155,6 +10211,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10324,6 +10381,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10491,6 +10549,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10660,6 +10719,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya pose le livre et va vers maman. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10827,6 +10887,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10996,6 +11057,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11163,6 +11225,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11332,6 +11395,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11515,6 +11579,7 @@
           <t>narrateur|Maya a les joues chaudes. Quel mot dit-on ? Avec un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11688,6 +11753,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11879,6 +11945,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12048,6 +12115,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12239,6 +12307,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12408,6 +12477,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12575,6 +12645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12744,6 +12815,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12911,6 +12983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13080,6 +13153,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya range la dînette un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13247,6 +13321,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13416,6 +13491,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13607,6 +13683,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13777,6 +13854,7 @@
 maman|Je t'ai entendu. Papa aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13944,6 +14022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14113,6 +14192,7 @@
 narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14280,6 +14360,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14449,6 +14530,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya serre la main de maman, tout doux. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14616,6 +14698,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14785,6 +14868,7 @@
 narrateur|Elle sourit. Elle invite à partager.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14976,6 +15060,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15145,6 +15230,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15312,6 +15398,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15481,6 +15568,7 @@
 narrateur|Elle sourit. Elle invite à partager. Maya boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15648,6 +15736,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15817,6 +15906,7 @@
 narrateur|Elle sourit. Elle invite à partager. On écoute le silence une seconde. Maya est assise. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15984,6 +16074,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16002,7 +16093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16026,6 +16117,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16227,6 +16332,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
